--- a/it_forms/040_superuser_access_request_form--it_forms.xlsx
+++ b/it_forms/040_superuser_access_request_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -650,8 +650,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,12 +679,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'superuser',_'label':_'superuser'}</t>
+          <t>superuser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Superuser', 'label': 'Superuser'}</t>
+          <t>Superuser</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'developer',_'label':_'developer'}</t>
+          <t>developer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Developer', 'label': 'Developer'}</t>
+          <t>Developer</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'it_admin',_'label':_'it_admin'}</t>
+          <t>it_admin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'IT Admin', 'label': 'IT Admin'}</t>
+          <t>IT Admin</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'it_admin',_'label':_'it_admin'}</t>
+          <t>it_admin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'IT Admin', 'label': 'IT Admin'}</t>
+          <t>IT Admin</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'director',_'label':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Director', 'label': 'Director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'manager',_'label':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Manager', 'label': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
